--- a/JsonConverter/ExcelFiles/OO_CookingTool.xlsx
+++ b/JsonConverter/ExcelFiles/OO_CookingTool.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,16 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <name val="?? ??"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +60,11 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -75,6 +88,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -634,6 +653,41 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Julgu</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>절구</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>쌀을 찧어 떡으로 만드는 조리도구입니다.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Ing_Rice_01</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>narration_tutorial_14</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Julgu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/OO_CookingTool.xlsx
+++ b/JsonConverter/ExcelFiles/OO_CookingTool.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ing_Rice_01|Ing_Kimch_01</t>
+          <t>Ing_Rice_01|Ing_Kimch_01|OO_CarrotStarch_1</t>
         </is>
       </c>
       <c r="E4" t="n">
